--- a/artfynd/A 54462-2025 artfynd.xlsx
+++ b/artfynd/A 54462-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130057102</v>
+        <v>130057101</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>79113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040162</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402118</v>
+        <v>402029</v>
       </c>
       <c r="R2" t="n">
-        <v>6706290</v>
+        <v>6706296</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,7 +775,7 @@
         <v>130057111</v>
       </c>
       <c r="B3" t="n">
-        <v>83051</v>
+        <v>83057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130057101</v>
+        <v>130057102</v>
       </c>
       <c r="B4" t="n">
-        <v>79112</v>
+        <v>92041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6040162</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402029</v>
+        <v>402118</v>
       </c>
       <c r="R4" t="n">
-        <v>6706296</v>
+        <v>6706290</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -949,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,7 +970,7 @@
         <v>130057112</v>
       </c>
       <c r="B5" t="n">
-        <v>83051</v>
+        <v>83057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>130057089</v>
       </c>
       <c r="B6" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>130057096</v>
       </c>
       <c r="B7" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>130057110</v>
       </c>
       <c r="B8" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>130057104</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>130057105</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54462-2025 artfynd.xlsx
+++ b/artfynd/A 54462-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130057111</v>
+        <v>130057101</v>
       </c>
       <c r="B2" t="n">
-        <v>83065</v>
+        <v>79119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402207</v>
+        <v>402029</v>
       </c>
       <c r="R2" t="n">
-        <v>6706447</v>
+        <v>6706296</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130057101</v>
+        <v>130057102</v>
       </c>
       <c r="B3" t="n">
-        <v>79119</v>
+        <v>92057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6040162</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402029</v>
+        <v>402118</v>
       </c>
       <c r="R3" t="n">
-        <v>6706296</v>
+        <v>6706290</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130057102</v>
+        <v>130057111</v>
       </c>
       <c r="B4" t="n">
-        <v>92057</v>
+        <v>83065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040162</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402118</v>
+        <v>402207</v>
       </c>
       <c r="R4" t="n">
-        <v>6706290</v>
+        <v>6706447</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -948,7 +949,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54462-2025 artfynd.xlsx
+++ b/artfynd/A 54462-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130057101</v>
+        <v>130057111</v>
       </c>
       <c r="B2" t="n">
-        <v>79119</v>
+        <v>83065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402029</v>
+        <v>402207</v>
       </c>
       <c r="R2" t="n">
-        <v>6706296</v>
+        <v>6706447</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130057102</v>
+        <v>130057101</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>79119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040162</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402118</v>
+        <v>402029</v>
       </c>
       <c r="R3" t="n">
-        <v>6706290</v>
+        <v>6706296</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130057111</v>
+        <v>130057102</v>
       </c>
       <c r="B4" t="n">
-        <v>83065</v>
+        <v>92059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6040162</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402207</v>
+        <v>402118</v>
       </c>
       <c r="R4" t="n">
-        <v>6706447</v>
+        <v>6706290</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -949,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130057089</v>
+        <v>130057096</v>
       </c>
       <c r="B6" t="n">
-        <v>97077</v>
+        <v>91605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402359</v>
+        <v>402393</v>
       </c>
       <c r="R6" t="n">
-        <v>6706523</v>
+        <v>6706564</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130057096</v>
+        <v>130057089</v>
       </c>
       <c r="B7" t="n">
-        <v>91603</v>
+        <v>97079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402393</v>
+        <v>402359</v>
       </c>
       <c r="R7" t="n">
-        <v>6706564</v>
+        <v>6706523</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 54462-2025 artfynd.xlsx
+++ b/artfynd/A 54462-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130057111</v>
+        <v>130057102</v>
       </c>
       <c r="B2" t="n">
-        <v>83065</v>
+        <v>92146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6040162</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402207</v>
+        <v>402118</v>
       </c>
       <c r="R2" t="n">
-        <v>6706447</v>
+        <v>6706290</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,32 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130057101</v>
+        <v>130057111</v>
       </c>
       <c r="B3" t="n">
-        <v>79119</v>
+        <v>83150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402029</v>
+        <v>402207</v>
       </c>
       <c r="R3" t="n">
-        <v>6706296</v>
+        <v>6706447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130057102</v>
+        <v>130057101</v>
       </c>
       <c r="B4" t="n">
-        <v>92059</v>
+        <v>79204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040162</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402118</v>
+        <v>402029</v>
       </c>
       <c r="R4" t="n">
-        <v>6706290</v>
+        <v>6706296</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -948,7 +949,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,7 +970,7 @@
         <v>130057112</v>
       </c>
       <c r="B5" t="n">
-        <v>83065</v>
+        <v>83150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130057096</v>
+        <v>130057089</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
+        <v>97166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402393</v>
+        <v>402359</v>
       </c>
       <c r="R6" t="n">
-        <v>6706564</v>
+        <v>6706523</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1161,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130057089</v>
+        <v>130057096</v>
       </c>
       <c r="B7" t="n">
-        <v>97079</v>
+        <v>91692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402359</v>
+        <v>402393</v>
       </c>
       <c r="R7" t="n">
-        <v>6706523</v>
+        <v>6706564</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1261,7 +1261,7 @@
         <v>130057110</v>
       </c>
       <c r="B8" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>130057104</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130057109</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>130057105</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
